--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_accesspath/lang_accesspath__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_accesspath/lang_accesspath__ui__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Nhận được qua nhiệm vụ</t>
+          <t>Nhận được từ nhiệm vụ</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Nhận được khi hoàn thành Dangerous Sampling lần đầu</t>
+          <t>Nhận được từ lần đầu vượt ải Dangerous Sampling</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Nhận được từ thử thách Tacet Field-Medium</t>
+          <t>Nhận được từ thử thách Tổ Tacet - Cấp Trung</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Nhận được qua thử thách Thunder Squama</t>
+          <t>Nhận được từ thử thách Thunder Squama</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Nhận được qua thử thách Mourning Aix</t>
+          <t>Nhận được từ thử thách Mourning Aix</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Nhận được qua thử thách Inferno Rider</t>
+          <t>Nhận được từ thử thách Inferno Rider</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Nhận được qua thử thách Feilian Beringal</t>
+          <t>Nhận được từ thử thách Feilian Beringal</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Nhận được từ thử thách Vịt Bất Diệt</t>
+          <t>Nhận được từ thử thách Impermanence Heron</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Nhận được qua thử thách Gleamtender</t>
+          <t>Nhận được từ thử thách Gleamtender</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Nhận được qua thử thách Seatrail Narwhal</t>
+          <t>Nhận được từ thử thách Seatrail Narwhal</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Nhận được qua thử thách Scar</t>
+          <t>Nhận được từ thử thách Scar</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Nhận từ Crownless - Thử thách Prime</t>
+          <t>Nhận được từ thử thách Crownless - Prime</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Nhận được qua khám phá Huanglong</t>
+          <t>Nhận được từ khám phá Huanglong</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Rơi từ động vật hoang dã</t>
+          <t>Rơi từ quái thú hoang dã</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Nhận được qua câu cá</t>
+          <t>Nhận được từ câu cá</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Nhận được qua bắt côn trùng</t>
+          <t>Nhận được từ bắt côn trùng</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Phổ biến tại: Hẻm Núi Tâm Linh</t>
+          <t>Thường thấy ở: Gorges of Spirit</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Chủ yếu tìm thấy tại: Central Plains</t>
+          <t>Thường xuất hiện tại: Central Plains</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Phổ biến tại: Tiancheng</t>
+          <t>Thường thấy ở: Tiancheng</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Chủ yếu tìm thấy tại: Desorock Highlands</t>
+          <t>Thường thấy ở: Desorock Highlands</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Chủ yếu tìm thấy tại: Norfall Barrens</t>
+          <t>Thường thấy ở: Norfall Barrens</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Chủ yếu tìm thấy tại: Wasted Metropolis</t>
+          <t>Thường thấy ở: Wasted Metropolis</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Thường thấy ở: Hukou, Tiger's Maw</t>
+          <t>Thường thấy ở: Hukou, the Tiger's Maw</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Chủ yếu tìm thấy tại: Forsaken Abundance</t>
+          <t>Thường thấy ở: Forsaken Abundance</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Thường xuất hiện tại: Dim Forest</t>
+          <t>Thường thấy ở: Dim Forest</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Chủ yếu xuất hiện ở: Bãi Lầy Whining Aix</t>
+          <t>Thường thấy ở: Whining Aix's Mire</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Chủ yếu tìm thấy tại: Black Shores</t>
+          <t>Thường xuất hiện tại: Black Shores</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>Nấu ăn</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Rơi Discord hạng Chuẩn</t>
+          <t>Vật phẩm rơi từ Tacet Discord Hạng Chuẩn</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Rơi từ Discord Class Elite</t>
+          <t>Rơi từ Tacet Discord hạng Cao Cấp</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Vật phẩm rơi từ Sinh Vật Đột Biến Tiêu Chuẩn Class</t>
+          <t>Vật phẩm rơi từ Sinh Vật Đột Biến Hạng Chuẩn</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Quái Vật Mutant Class Elite rơi ra</t>
+          <t>Rơi từ sinh vật đột biến Hạng Cao Cấp</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Rơi từ kẻ địch Human cấp Chuẩn</t>
+          <t>Vật phẩm rơi từ Người Hạng Chuẩn</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Rơi từ kẻ địch Human cấp Tinh Anh</t>
+          <t>Rơi từ người Hạng Cao Cấp</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Exchange qua Hệ Thống Exchange Chung</t>
+          <t>Đổi từ Sàn Giao Dịch Liên Kết</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Exchange qua Interference Exchange</t>
+          <t>Đổi từ Sàn Giao Dịch Nhiễu Loạn</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Đổi tại Cửa hàng Lưu niệm</t>
+          <t>Đổi từ Cửa Hàng Lưu Niệm</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Đổi từ Nhà buôn đồ cổ - Tiancheng</t>
+          <t>Đổi từ Thương Nhân Cổ Vật - Tiancheng</t>
         </is>
       </c>
     </row>
